--- a/nriss-patch-2/ig/ValueSet-fr-vs-location-body-structure-document.xlsx
+++ b/nriss-patch-2/ig/ValueSet-fr-vs-location-body-structure-document.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
